--- a/References/Hybrid SDLC Agile Templates/TGI - NONOS - DAVID - Hybrid SDLC Agile.xlsx
+++ b/References/Hybrid SDLC Agile Templates/TGI - NONOS - DAVID - Hybrid SDLC Agile.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="351">
   <si>
     <t>Template Name</t>
   </si>
@@ -924,6 +924,12 @@
   </si>
   <si>
     <t>Use the matrix as the cross-department reporting view. Milestone marks the primary owning department and Waiting is the recommended initial state; replace these with current status or target week as planning progresses. Imported Sub-Tasks remain the source of progress percentages.</t>
+  </si>
+  <si>
+    <t>Parallel planning</t>
+  </si>
+  <si>
+    <t>Independent departmental readiness checkpoints run in parallel after the target workflow is approved. LINK HUB business processes also run as parallel workstreams; design/build/QA/UAT/release gates inside each process remain sequential.</t>
   </si>
   <si>
     <t>Task Board</t>
@@ -14922,8 +14928,12 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2"/>
@@ -15692,7 +15702,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -15700,30 +15710,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -15731,13 +15741,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>205</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -15745,41 +15755,41 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -16960,22 +16970,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -16989,7 +16999,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -17000,30 +17010,30 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -17031,7 +17041,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
